--- a/outputs/monitor_xlsx/20260222.xlsx
+++ b/outputs/monitor_xlsx/20260222.xlsx
@@ -473,6 +473,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -536,10 +537,6 @@
           <t>+0.37%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -562,10 +559,6 @@
           <t>+1.68%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -588,10 +581,6 @@
           <t>+0.16%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -614,10 +603,6 @@
           <t>+1.07%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -640,10 +625,6 @@
           <t>-5.64%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -661,7 +642,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>105.98億</t>
@@ -699,7 +679,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>39.16億</t>
@@ -710,8 +689,6 @@
           <t>195.78億</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -729,15 +706,11 @@
           <t>150.22%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>164.08%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -755,11 +728,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -777,15 +745,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>None口</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -803,7 +767,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>24.77億</t>
@@ -853,6 +816,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -908,10 +872,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1033,7 +994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1067,6 +1028,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1140,40 +1102,35 @@
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1199,12 +1156,7 @@
       <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1230,12 +1182,7 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1261,12 +1208,7 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1292,12 +1234,7 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1323,12 +1260,7 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1354,12 +1286,7 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1385,12 +1312,7 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1416,12 +1338,7 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1447,12 +1364,7 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1478,12 +1390,7 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1509,12 +1416,7 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1540,12 +1442,7 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1571,12 +1468,7 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1602,12 +1494,7 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1633,12 +1520,7 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1664,12 +1546,7 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
